--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_61_R7.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_61_R7.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5822</v>
+        <v>5.4361</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7349</v>
+        <v>5.6302</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8473</v>
+        <v>-0.1942</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7583</v>
+        <v>2.4509</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.0755</v>
+        <v>1.2965</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8339</v>
+        <v>1.1544</v>
       </c>
       <c r="J2" t="n">
-        <v>2.1585</v>
+        <v>3.5732</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.418</v>
+        <v>1.4151</v>
       </c>
       <c r="L2" t="n">
-        <v>3.5765</v>
+        <v>2.1581</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4002</v>
+        <v>-1.1222</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3424</v>
+        <v>-0.1186</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7426</v>
+        <v>-1.0037</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0738</v>
+        <v>0.0727</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.55</v>
+        <v>0.0002</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6238</v>
+        <v>0.0725</v>
       </c>
       <c r="V2" t="n">
-        <v>2.2862</v>
+        <v>2.6805</v>
       </c>
       <c r="W2" t="n">
-        <v>2.2862</v>
+        <v>3.2166</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H. DIALLO</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5691</v>
+        <v>4.7226</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7853</v>
+        <v>3.0769</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2162</v>
+        <v>1.6456</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6146</v>
+        <v>1.7583</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1498</v>
+        <v>-1.0755</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5352</v>
+        <v>2.8339</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0359</v>
+        <v>2.1585</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4605</v>
+        <v>-1.418</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5754</v>
+        <v>3.5765</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4214</v>
+        <v>-0.4002</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6893</v>
+        <v>0.3424</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.1107</v>
+        <v>-0.7426</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>2.207</v>
+        <v>0.2142</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5534</v>
+        <v>-0.208</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.4222</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2525</v>
+        <v>2.2862</v>
       </c>
       <c r="W3" t="n">
-        <v>1.3558</v>
+        <v>2.2862</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>H. DIALLO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2265</v>
+        <v>3.4627</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8911</v>
+        <v>3.9478</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6646</v>
+        <v>-0.4851</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4509</v>
+        <v>2.6146</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2965</v>
+        <v>3.1498</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1544</v>
+        <v>-0.5352</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5732</v>
+        <v>3.0359</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4151</v>
+        <v>2.4605</v>
       </c>
       <c r="L4" t="n">
-        <v>2.1581</v>
+        <v>0.5754</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1222</v>
+        <v>-0.4214</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1186</v>
+        <v>0.6893</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0037</v>
+        <v>-1.1107</v>
       </c>
       <c r="P4" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1369</v>
+        <v>1.1007</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7389</v>
+        <v>0.7158</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.398</v>
+        <v>0.3848</v>
       </c>
       <c r="V4" t="n">
-        <v>2.6805</v>
+        <v>-0.2525</v>
       </c>
       <c r="W4" t="n">
-        <v>3.2166</v>
+        <v>1.3558</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5361</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5221</v>
+        <v>1.3198</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7174</v>
+        <v>1.4815</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1953</v>
+        <v>-0.1617</v>
       </c>
       <c r="G5" t="n">
         <v>1.8581</v>
@@ -844,13 +844,13 @@
         <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2544</v>
+        <v>0.0521</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3383</v>
+        <v>0.1024</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0839</v>
+        <v>-0.0503</v>
       </c>
       <c r="V5" t="n">
         <v>-1.7501</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2141</v>
+        <v>0.2543</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3727</v>
+        <v>-0.7948</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5868</v>
+        <v>1.0491</v>
       </c>
       <c r="G6" t="n">
         <v>-1.0888</v>
@@ -922,13 +922,13 @@
         <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8364</v>
+        <v>0.8766</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7468</v>
+        <v>-0.1689</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5832</v>
+        <v>1.0455</v>
       </c>
       <c r="V6" t="n">
         <v>0.9304</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1224</v>
+        <v>0.1896</v>
       </c>
       <c r="E7" t="n">
         <v>0.0672</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0552</v>
+        <v>0.1224</v>
       </c>
       <c r="G7" t="n">
         <v>0.0029</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1195</v>
+        <v>0.1867</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1195</v>
+        <v>0.1867</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>M. NOWELL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0419</v>
+        <v>0.1615</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6755</v>
+        <v>0.098</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6336</v>
+        <v>0.0635</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7477</v>
+        <v>-0.4076</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0625</v>
+        <v>-0.3072</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8102</v>
+        <v>-0.1004</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7662</v>
+        <v>0.1608</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9439</v>
+        <v>0.0504</v>
       </c>
       <c r="L8" t="n">
-        <v>2.7101</v>
+        <v>0.1104</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0185</v>
+        <v>-0.5684</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1186</v>
+        <v>-0.3577</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8999</v>
+        <v>-0.2108</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5531</v>
+        <v>0.1052</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4753</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>1.0284</v>
+        <v>0.168</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6468</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6468</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. NOWELL</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2499</v>
+        <v>-0.1203</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2126</v>
+        <v>-1.4514</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0373</v>
+        <v>1.3311</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4076</v>
+        <v>0.7477</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3072</v>
+        <v>-1.0625</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1004</v>
+        <v>1.8102</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1608</v>
+        <v>1.7662</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0504</v>
+        <v>-0.9439</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1104</v>
+        <v>2.7101</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5684</v>
+        <v>-1.0185</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3577</v>
+        <v>-0.1186</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2108</v>
+        <v>-0.8999</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4639</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3062</v>
+        <v>0.4747</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3734</v>
+        <v>-0.2513</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0672</v>
+        <v>0.726</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.6468</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.6468</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. DIOP</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5087</v>
+        <v>-0.2087</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2805</v>
+        <v>-0.5199</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7892</v>
+        <v>0.3112</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0331</v>
+        <v>-1.1729</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4357</v>
+        <v>-0.4201</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4688</v>
+        <v>-0.7528</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4751</v>
+        <v>-0.6655</v>
       </c>
       <c r="K10" t="n">
-        <v>1.3647</v>
+        <v>-0.7023</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1104</v>
+        <v>0.0368</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5082</v>
+        <v>-0.5074</v>
       </c>
       <c r="N10" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.2822</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.5792</v>
+        <v>-0.7896</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3104</v>
+        <v>0.2684</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9831</v>
+        <v>0.1456</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3273</v>
+        <v>0.1228</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>K. DIOP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7306</v>
+        <v>-0.9827</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8737</v>
+        <v>-0.1599</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1432</v>
+        <v>-0.8228</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1729</v>
+        <v>-0.0331</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4201</v>
+        <v>1.4357</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7528</v>
+        <v>-1.4688</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6655</v>
+        <v>1.4751</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7023</v>
+        <v>1.3647</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0368</v>
+        <v>0.1104</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5074</v>
+        <v>-1.5082</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2822</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7896</v>
+        <v>-1.5792</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6959</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2535</v>
+        <v>0.8364</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2082</v>
+        <v>0.5427</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0452</v>
+        <v>0.2937</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6135</v>
+        <v>-1.9765</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1293</v>
+        <v>-1.862</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4842</v>
+        <v>-0.1145</v>
       </c>
       <c r="G12" t="n">
         <v>-1.5409</v>
@@ -1390,13 +1390,13 @@
         <v>1.6237</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8895999999999999</v>
+        <v>-0.2526</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2434</v>
+        <v>0.0239</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6462</v>
+        <v>-0.2765</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6468</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.595</v>
+        <v>-4.268</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.1873</v>
+        <v>-1.9946</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.4077</v>
+        <v>-2.2733</v>
       </c>
       <c r="G13" t="n">
         <v>-0.8445</v>
@@ -1468,13 +1468,13 @@
         <v>0.232</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.449</v>
+        <v>-0.1219</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.224</v>
+        <v>-0.0314</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2249</v>
+        <v>-0.0905</v>
       </c>
       <c r="V13" t="n">
         <v>-1.214</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.496799999999999</v>
+        <v>7.990399999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>6.0253</v>
+        <v>7.519</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4716</v>
+        <v>0.4713000000000003</v>
       </c>
       <c r="G14" t="n">
         <v>4.344699999999999</v>
@@ -1516,7 +1516,7 @@
         <v>5.6662</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.321400000000001</v>
+        <v>-1.3214</v>
       </c>
       <c r="J14" t="n">
         <v>11.6171</v>
@@ -1528,13 +1528,13 @@
         <v>6.6073</v>
       </c>
       <c r="M14" t="n">
-        <v>-7.272399999999998</v>
+        <v>-7.272399999999999</v>
       </c>
       <c r="N14" t="n">
         <v>0.6561000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-7.9288</v>
+        <v>-7.928800000000002</v>
       </c>
       <c r="P14" t="n">
         <v>-1.1597</v>
@@ -1546,16 +1546,16 @@
         <v>11.5979</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3194</v>
+        <v>3.8132</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6852000000000001</v>
+        <v>0.8082</v>
       </c>
       <c r="U14" t="n">
         <v>3.0049</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9925999999999999</v>
+        <v>0.992599999999999</v>
       </c>
       <c r="W14" t="n">
         <v>7.8512</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.8791</v>
+        <v>5.8918</v>
       </c>
       <c r="E15" t="n">
-        <v>6.6311</v>
+        <v>5.9234</v>
       </c>
       <c r="F15" t="n">
-        <v>0.248</v>
+        <v>-0.0316</v>
       </c>
       <c r="G15" t="n">
         <v>0.8121</v>
@@ -1624,13 +1624,13 @@
         <v>2.5515</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4071</v>
+        <v>0.4197</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6256</v>
+        <v>-0.0822</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7815</v>
+        <v>0.5019</v>
       </c>
       <c r="V15" t="n">
         <v>3.5002</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7643</v>
+        <v>3.3433</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6181</v>
+        <v>3.2078</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1463</v>
+        <v>0.1355</v>
       </c>
       <c r="G16" t="n">
         <v>2.1116</v>
@@ -1702,13 +1702,13 @@
         <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7569</v>
+        <v>-0.1779</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1044</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3475</v>
+        <v>0.3367</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6778999999999999</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. ANDERSON</t>
+          <t>K. KONDIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5572</v>
+        <v>2.2506</v>
       </c>
       <c r="E17" t="n">
-        <v>3.823</v>
+        <v>3.3212</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2659</v>
+        <v>-1.0705</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4698</v>
+        <v>2.4844</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7876</v>
+        <v>-0.7778</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3178</v>
+        <v>3.2622</v>
       </c>
       <c r="J17" t="n">
-        <v>2.7178</v>
+        <v>3.064</v>
       </c>
       <c r="K17" t="n">
+        <v>0.5881999999999999</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.4759</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0.5796</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-1.366</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.7863</v>
+      </c>
+      <c r="P17" t="n">
         <v>0.9278</v>
       </c>
-      <c r="L17" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="M17" t="n">
-        <v>-2.248</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-0.1401</v>
-      </c>
-      <c r="O17" t="n">
-        <v>-2.1078</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.8556</v>
-      </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4457</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1053</v>
+        <v>-0.047</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3405</v>
+        <v>-0.0424</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.214</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. KONDIC</t>
+          <t>J. ANDERSON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8238</v>
+        <v>1.5685</v>
       </c>
       <c r="E18" t="n">
-        <v>3.0853</v>
+        <v>2.6435</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2614</v>
+        <v>-1.075</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4844</v>
+        <v>0.4698</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7778</v>
+        <v>0.7876</v>
       </c>
       <c r="I18" t="n">
-        <v>3.2622</v>
+        <v>-0.3178</v>
       </c>
       <c r="J18" t="n">
-        <v>3.064</v>
+        <v>2.7178</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.9278</v>
       </c>
       <c r="L18" t="n">
-        <v>2.4759</v>
+        <v>1.79</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5796</v>
+        <v>-2.248</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.366</v>
+        <v>-0.1401</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7863</v>
+        <v>-2.1078</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5162</v>
+        <v>0.4571</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2829</v>
+        <v>-0.0743</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2333</v>
+        <v>0.5313</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.6083</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. SANLI</t>
+          <t>A. ABASS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.64</v>
+        <v>-0.2675</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2194</v>
+        <v>-0.3734</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4206</v>
+        <v>0.1058</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5528</v>
+        <v>0.4095</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3085</v>
+        <v>0.1585</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2443</v>
+        <v>0.251</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8602</v>
+        <v>0.1808</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8234</v>
+        <v>0.0336</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0368</v>
+        <v>0.1472</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3074</v>
+        <v>0.2287</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5149</v>
+        <v>0.1249</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2075</v>
+        <v>0.1038</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4274</v>
+        <v>-0.3007</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.224</v>
+        <v>-0.5542</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2034</v>
+        <v>0.2535</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3943</v>
+        <v>-1.0722</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ABASS</t>
+          <t>S. SANLI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7444</v>
+        <v>-0.6736</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4913</v>
+        <v>-0.2194</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2531</v>
+        <v>-0.4542</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4095</v>
+        <v>0.5528</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1585</v>
+        <v>0.3085</v>
       </c>
       <c r="I20" t="n">
-        <v>0.251</v>
+        <v>0.2443</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1808</v>
+        <v>0.8602</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0336</v>
+        <v>0.8234</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1472</v>
+        <v>0.0368</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2287</v>
+        <v>-0.3074</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1249</v>
+        <v>-0.5149</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1038</v>
+        <v>0.2075</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6959</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7776</v>
+        <v>-0.461</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6721</v>
+        <v>-0.224</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1054</v>
+        <v>-0.237</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0722</v>
+        <v>0.3943</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. KABENGELE</t>
+          <t>M. WRIGHT IV</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.231</v>
+        <v>-1.1974</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9684</v>
+        <v>-0.4854</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2625</v>
+        <v>-0.712</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6149</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.461</v>
+        <v>1.9132</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1539</v>
+        <v>-1.1376</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4821</v>
+        <v>2.2373</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7324000000000001</v>
+        <v>1.8961</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2146</v>
+        <v>0.3412</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.097</v>
+        <v>-1.4616</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2714</v>
+        <v>0.0171</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3684</v>
+        <v>-1.4787</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.1598</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1598</v>
+        <v>-2.5515</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.6237</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3145</v>
+        <v>-0.5091</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2908</v>
+        <v>-0.7073</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0237</v>
+        <v>0.1981</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1418</v>
+        <v>-0.5361</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. WRIGHT IV</t>
+          <t>M. KABENGELE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4542</v>
+        <v>-1.7199</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9572000000000001</v>
+        <v>-0.6146</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4971</v>
+        <v>-1.1053</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7756999999999999</v>
+        <v>-0.6149</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9132</v>
+        <v>-0.461</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1376</v>
+        <v>-0.1539</v>
       </c>
       <c r="J22" t="n">
-        <v>2.2373</v>
+        <v>0.4821</v>
       </c>
       <c r="K22" t="n">
-        <v>1.8961</v>
+        <v>-0.7324000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3412</v>
+        <v>1.2146</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4616</v>
+        <v>-1.097</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0171</v>
+        <v>0.2714</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.4787</v>
+        <v>-1.3684</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9278</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.5515</v>
+        <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.766</v>
+        <v>0.1966</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1791</v>
+        <v>0.063</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5869</v>
+        <v>0.1336</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5361</v>
+        <v>-0.1418</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="23">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.546</v>
+        <v>-3.7318</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.9518</v>
+        <v>-4.3056</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4058</v>
+        <v>0.5738</v>
       </c>
       <c r="G24" t="n">
         <v>-4.2618</v>
@@ -2326,13 +2326,13 @@
         <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>0.06900000000000001</v>
+        <v>-0.1169</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1221</v>
+        <v>-0.2317</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0532</v>
+        <v>0.1149</v>
       </c>
       <c r="V24" t="n">
         <v>0.6468</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.305199999999999</v>
+        <v>-7.7877</v>
       </c>
       <c r="E25" t="n">
-        <v>-9.2165</v>
+        <v>-8.7447</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9114</v>
+        <v>0.9571</v>
       </c>
       <c r="G25" t="n">
         <v>-6.1663</v>
@@ -2404,13 +2404,13 @@
         <v>1.3917</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.608</v>
+        <v>-0.0905</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.0297</v>
+        <v>-0.5579</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4217</v>
+        <v>0.4674</v>
       </c>
       <c r="V25" t="n">
         <v>0.7886</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.496999999999998</v>
+        <v>-4.924300000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.4713000000000012</v>
+        <v>-0.4713999999999992</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.025399999999999</v>
+        <v>-4.4527</v>
       </c>
       <c r="G26" t="n">
         <v>-4.3447</v>
@@ -2482,13 +2482,13 @@
         <v>12.7576</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.3195</v>
+        <v>-0.7468</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.0047</v>
+        <v>-3.0049</v>
       </c>
       <c r="U26" t="n">
-        <v>0.6853</v>
+        <v>2.258</v>
       </c>
       <c r="V26" t="n">
         <v>-0.9925999999999999</v>
